--- a/src/cassy/additional_data/templates/template sdic_bolt.xlsx
+++ b/src/cassy/additional_data/templates/template sdic_bolt.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://niering-my.sharepoint.com/personal/d_falco_nier_it/Documents/Documenti/GitHub/KAISER/src/kaiser/additional_data/templates/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\DATA\laghida\Documents\GitLab\cassy\src\cassy\additional_data\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{6384A9F2-9A9E-444B-9CDA-7634A0AAFF72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E2DF39E5-90BC-4B5B-86B9-84A474572AA4}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F34B6F21-9047-474A-8DB2-E08C5AB5F876}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-57720" yWindow="1725" windowWidth="29040" windowHeight="15840" xr2:uid="{1B14086C-9772-43C7-BBF2-FDC7401A2E4E}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18120" activeTab="2" xr2:uid="{1B14086C-9772-43C7-BBF2-FDC7401A2E4E}"/>
   </bookViews>
   <sheets>
-    <sheet name="WORD template" sheetId="2" r:id="rId1"/>
-    <sheet name="SA template" sheetId="1" r:id="rId2"/>
-    <sheet name="Fatigue template" sheetId="3" r:id="rId3"/>
+    <sheet name="Input_template" sheetId="2" r:id="rId1"/>
+    <sheet name="SA_template" sheetId="1" r:id="rId2"/>
+    <sheet name="Fatigue_template" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -1329,6 +1329,33 @@
     <xf numFmtId="11" fontId="3" fillId="2" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="51" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1364,31 +1391,118 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="51" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="43" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1426,124 +1540,10 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="45" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Normale" xfId="0" builtinId="0"/>
-    <cellStyle name="Percentuale" xfId="1" builtinId="5"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
   <dxfs count="16">
     <dxf>
@@ -1709,7 +1709,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - Tema 2022">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
     <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
@@ -2006,15 +2006,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C422058-0711-4AAE-BBC4-1DEA1ED115C1}">
   <dimension ref="A1:H9"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.84375" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="2" width="15.85546875" style="1" customWidth="1"/>
-    <col min="3" max="5" width="24.85546875" style="1" customWidth="1"/>
-    <col min="6" max="8" width="12.85546875" style="35" customWidth="1"/>
-    <col min="9" max="16384" width="8.85546875" style="1"/>
+    <col min="1" max="2" width="15.84375" style="1" customWidth="1"/>
+    <col min="3" max="5" width="24.84375" style="1" customWidth="1"/>
+    <col min="6" max="8" width="12.84375" style="35" customWidth="1"/>
+    <col min="9" max="16384" width="8.84375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A1" s="41" t="s">
         <v>0</v>
       </c>
@@ -2026,7 +2026,7 @@
       <c r="G1" s="43"/>
       <c r="H1" s="44"/>
     </row>
-    <row r="2" spans="1:8" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A2" s="68" t="s">
         <v>1</v>
       </c>
@@ -2038,7 +2038,7 @@
       <c r="G2" s="53"/>
       <c r="H2" s="54"/>
     </row>
-    <row r="3" spans="1:8" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:8" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A3" s="70" t="s">
         <v>3</v>
       </c>
@@ -2050,7 +2050,7 @@
       <c r="G3" s="56"/>
       <c r="H3" s="57"/>
     </row>
-    <row r="4" spans="1:8" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" customFormat="1" x14ac:dyDescent="0.4">
       <c r="A4" s="70" t="s">
         <v>5</v>
       </c>
@@ -2062,7 +2062,7 @@
       <c r="G4" s="59"/>
       <c r="H4" s="60"/>
     </row>
-    <row r="5" spans="1:8" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:8" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A5" s="72" t="s">
         <v>7</v>
       </c>
@@ -2074,14 +2074,14 @@
       <c r="G5" s="66"/>
       <c r="H5" s="67"/>
     </row>
-    <row r="6" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A6" s="35"/>
       <c r="B6" s="35"/>
       <c r="C6" s="35"/>
       <c r="D6" s="35"/>
       <c r="E6" s="35"/>
     </row>
-    <row r="7" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A7" s="49" t="s">
         <v>49</v>
       </c>
@@ -2093,7 +2093,7 @@
       <c r="G7" s="50"/>
       <c r="H7" s="51"/>
     </row>
-    <row r="8" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:8" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A8" s="47" t="s">
         <v>41</v>
       </c>
@@ -2113,7 +2113,7 @@
       <c r="G8" s="75"/>
       <c r="H8" s="76"/>
     </row>
-    <row r="9" spans="1:8" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:8" ht="21" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A9" s="48"/>
       <c r="B9" s="46"/>
       <c r="C9" s="62"/>
@@ -2168,130 +2168,125 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{092643CF-4C0B-4C96-BB86-6BCB65C4831B}">
   <dimension ref="A1:O5"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.84375" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="15.140625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="11.42578125" style="1" customWidth="1"/>
-    <col min="3" max="4" width="14.7109375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="9.28515625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="8.85546875" style="1" customWidth="1"/>
-    <col min="7" max="7" width="11.5703125" style="1" customWidth="1"/>
-    <col min="8" max="8" width="8.5703125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="10.140625" style="1" customWidth="1"/>
-    <col min="11" max="11" width="17.7109375" style="1" customWidth="1"/>
-    <col min="12" max="13" width="10.5703125" style="1" customWidth="1"/>
-    <col min="14" max="16384" width="8.85546875" style="1"/>
+    <col min="1" max="1" width="15.15234375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="11.3828125" style="1" customWidth="1"/>
+    <col min="3" max="4" width="14.69140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="9.3046875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="8.84375" style="1" customWidth="1"/>
+    <col min="7" max="7" width="11.53515625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="8.53515625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="13.53515625" style="1" customWidth="1"/>
+    <col min="10" max="10" width="10.15234375" style="1" customWidth="1"/>
+    <col min="11" max="11" width="17.69140625" style="1" customWidth="1"/>
+    <col min="12" max="13" width="10.53515625" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="8.84375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="90" t="s">
+    <row r="1" spans="1:15" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A1" s="77" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="91"/>
-      <c r="C1" s="91"/>
-      <c r="D1" s="91"/>
-      <c r="E1" s="91"/>
-      <c r="F1" s="91"/>
-      <c r="G1" s="91"/>
-      <c r="H1" s="91"/>
-      <c r="I1" s="91"/>
-      <c r="J1" s="91"/>
-      <c r="K1" s="91"/>
-      <c r="L1" s="91"/>
-      <c r="M1" s="91"/>
-      <c r="N1" s="91"/>
-      <c r="O1" s="92"/>
+      <c r="B1" s="78"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
+      <c r="F1" s="78"/>
+      <c r="G1" s="78"/>
+      <c r="H1" s="78"/>
+      <c r="I1" s="78"/>
+      <c r="J1" s="78"/>
+      <c r="K1" s="78"/>
+      <c r="L1" s="78"/>
+      <c r="M1" s="78"/>
+      <c r="N1" s="78"/>
+      <c r="O1" s="79"/>
     </row>
-    <row r="2" spans="1:15" customFormat="1" ht="54" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="93" t="s">
+    <row r="2" spans="1:15" customFormat="1" ht="54" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="80" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="94"/>
-      <c r="C2" s="95"/>
-      <c r="D2" s="94"/>
-      <c r="E2" s="94"/>
-      <c r="F2" s="94"/>
-      <c r="G2" s="96"/>
-      <c r="H2" s="97" t="s">
+      <c r="B2" s="81"/>
+      <c r="C2" s="82"/>
+      <c r="D2" s="81"/>
+      <c r="E2" s="81"/>
+      <c r="F2" s="81"/>
+      <c r="G2" s="83"/>
+      <c r="H2" s="84" t="s">
         <v>2</v>
       </c>
-      <c r="I2" s="98"/>
-      <c r="J2" s="99"/>
-      <c r="K2" s="99"/>
-      <c r="L2" s="99"/>
-      <c r="M2" s="99"/>
-      <c r="N2" s="99"/>
-      <c r="O2" s="100"/>
+      <c r="I2" s="85"/>
+      <c r="J2" s="86"/>
+      <c r="K2" s="86"/>
+      <c r="L2" s="86"/>
+      <c r="M2" s="86"/>
+      <c r="N2" s="86"/>
+      <c r="O2" s="87"/>
     </row>
-    <row r="3" spans="1:15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="82" t="s">
+    <row r="3" spans="1:15" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="93" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="83"/>
-      <c r="C3" s="84"/>
-      <c r="D3" s="83"/>
-      <c r="E3" s="83"/>
-      <c r="F3" s="83"/>
-      <c r="G3" s="85"/>
-      <c r="H3" s="82" t="s">
+      <c r="B3" s="94"/>
+      <c r="C3" s="95"/>
+      <c r="D3" s="94"/>
+      <c r="E3" s="94"/>
+      <c r="F3" s="94"/>
+      <c r="G3" s="96"/>
+      <c r="H3" s="93" t="s">
         <v>4</v>
       </c>
-      <c r="I3" s="83"/>
-      <c r="J3" s="77"/>
-      <c r="K3" s="77"/>
-      <c r="L3" s="77"/>
-      <c r="M3" s="77"/>
-      <c r="N3" s="77"/>
-      <c r="O3" s="78"/>
+      <c r="I3" s="94"/>
+      <c r="J3" s="88"/>
+      <c r="K3" s="88"/>
+      <c r="L3" s="88"/>
+      <c r="M3" s="88"/>
+      <c r="N3" s="88"/>
+      <c r="O3" s="89"/>
     </row>
-    <row r="4" spans="1:15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="82" t="s">
+    <row r="4" spans="1:15" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="93" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="83"/>
-      <c r="C4" s="84"/>
-      <c r="D4" s="83"/>
-      <c r="E4" s="83"/>
-      <c r="F4" s="83"/>
-      <c r="G4" s="85"/>
-      <c r="H4" s="82" t="s">
+      <c r="B4" s="94"/>
+      <c r="C4" s="95"/>
+      <c r="D4" s="94"/>
+      <c r="E4" s="94"/>
+      <c r="F4" s="94"/>
+      <c r="G4" s="96"/>
+      <c r="H4" s="93" t="s">
         <v>6</v>
       </c>
-      <c r="I4" s="83"/>
-      <c r="J4" s="77"/>
-      <c r="K4" s="77"/>
-      <c r="L4" s="77"/>
-      <c r="M4" s="77"/>
-      <c r="N4" s="77"/>
-      <c r="O4" s="78"/>
+      <c r="I4" s="94"/>
+      <c r="J4" s="88"/>
+      <c r="K4" s="88"/>
+      <c r="L4" s="88"/>
+      <c r="M4" s="88"/>
+      <c r="N4" s="88"/>
+      <c r="O4" s="89"/>
     </row>
-    <row r="5" spans="1:15" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="86" t="s">
+    <row r="5" spans="1:15" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A5" s="97" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="87"/>
-      <c r="C5" s="88"/>
-      <c r="D5" s="88"/>
-      <c r="E5" s="88"/>
-      <c r="F5" s="88"/>
-      <c r="G5" s="89"/>
-      <c r="H5" s="79"/>
-      <c r="I5" s="80"/>
-      <c r="J5" s="80"/>
-      <c r="K5" s="80"/>
-      <c r="L5" s="80"/>
-      <c r="M5" s="80"/>
-      <c r="N5" s="80"/>
-      <c r="O5" s="81"/>
+      <c r="B5" s="98"/>
+      <c r="C5" s="99"/>
+      <c r="D5" s="99"/>
+      <c r="E5" s="99"/>
+      <c r="F5" s="99"/>
+      <c r="G5" s="100"/>
+      <c r="H5" s="90"/>
+      <c r="I5" s="91"/>
+      <c r="J5" s="91"/>
+      <c r="K5" s="91"/>
+      <c r="L5" s="91"/>
+      <c r="M5" s="91"/>
+      <c r="N5" s="91"/>
+      <c r="O5" s="92"/>
     </row>
   </sheetData>
   <mergeCells count="16">
-    <mergeCell ref="A1:O1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="C2:G2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="J2:O2"/>
     <mergeCell ref="J3:O3"/>
     <mergeCell ref="J4:O4"/>
     <mergeCell ref="H5:O5"/>
@@ -2303,6 +2298,11 @@
     <mergeCell ref="H4:I4"/>
     <mergeCell ref="A5:B5"/>
     <mergeCell ref="C5:G5"/>
+    <mergeCell ref="A1:O1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="C2:G2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="J2:O2"/>
   </mergeCells>
   <conditionalFormatting sqref="A1 P1:XFD5 A2:J4 A5:H5 A6:XFD1048576">
     <cfRule type="cellIs" dxfId="12" priority="4" operator="equal">
@@ -2323,115 +2323,115 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E691FB3C-A091-4158-83DB-901DAD7E0639}">
   <dimension ref="A1:J19"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.84375" defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="15.140625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="18.7109375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="22.28515625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="8.7109375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="10.140625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="13.5703125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="21.42578125" style="1" customWidth="1"/>
-    <col min="8" max="8" width="12.5703125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="15.15234375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="18.69140625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="22.3046875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="8.69140625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="10.15234375" style="1" customWidth="1"/>
+    <col min="6" max="6" width="13.53515625" style="1" customWidth="1"/>
+    <col min="7" max="7" width="21.3828125" style="1" customWidth="1"/>
+    <col min="8" max="8" width="12.53515625" style="1" customWidth="1"/>
     <col min="9" max="9" width="13" style="1" customWidth="1"/>
-    <col min="10" max="10" width="11.42578125" style="1" customWidth="1"/>
-    <col min="11" max="16384" width="8.85546875" style="1"/>
+    <col min="10" max="10" width="11.3828125" style="1" customWidth="1"/>
+    <col min="11" max="16384" width="8.84375" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="90" t="s">
+    <row r="1" spans="1:10" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A1" s="77" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="91"/>
-      <c r="C1" s="91"/>
-      <c r="D1" s="91"/>
-      <c r="E1" s="91"/>
-      <c r="F1" s="91"/>
-      <c r="G1" s="91"/>
-      <c r="H1" s="91"/>
-      <c r="I1" s="91"/>
-      <c r="J1" s="92"/>
+      <c r="B1" s="78"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
+      <c r="F1" s="78"/>
+      <c r="G1" s="78"/>
+      <c r="H1" s="78"/>
+      <c r="I1" s="78"/>
+      <c r="J1" s="79"/>
     </row>
-    <row r="2" spans="1:10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="101" t="s">
+    <row r="2" spans="1:10" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="141" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="102"/>
-      <c r="C2" s="105"/>
-      <c r="D2" s="106"/>
-      <c r="E2" s="107"/>
-      <c r="F2" s="101" t="s">
+      <c r="B2" s="142"/>
+      <c r="C2" s="145"/>
+      <c r="D2" s="146"/>
+      <c r="E2" s="147"/>
+      <c r="F2" s="141" t="s">
         <v>2</v>
       </c>
-      <c r="G2" s="102"/>
-      <c r="H2" s="108"/>
-      <c r="I2" s="109"/>
-      <c r="J2" s="110"/>
+      <c r="G2" s="142"/>
+      <c r="H2" s="148"/>
+      <c r="I2" s="149"/>
+      <c r="J2" s="150"/>
     </row>
-    <row r="3" spans="1:10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="103" t="s">
+    <row r="3" spans="1:10" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="143" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="104"/>
-      <c r="C3" s="111"/>
-      <c r="D3" s="112"/>
-      <c r="E3" s="113"/>
-      <c r="F3" s="103" t="s">
+      <c r="B3" s="144"/>
+      <c r="C3" s="151"/>
+      <c r="D3" s="152"/>
+      <c r="E3" s="153"/>
+      <c r="F3" s="143" t="s">
         <v>4</v>
       </c>
-      <c r="G3" s="104"/>
-      <c r="H3" s="111"/>
-      <c r="I3" s="112"/>
-      <c r="J3" s="113"/>
+      <c r="G3" s="144"/>
+      <c r="H3" s="151"/>
+      <c r="I3" s="152"/>
+      <c r="J3" s="153"/>
     </row>
-    <row r="4" spans="1:10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="103" t="s">
+    <row r="4" spans="1:10" customFormat="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="143" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="104"/>
-      <c r="C4" s="111"/>
-      <c r="D4" s="112"/>
-      <c r="E4" s="113"/>
-      <c r="F4" s="103" t="s">
+      <c r="B4" s="144"/>
+      <c r="C4" s="151"/>
+      <c r="D4" s="152"/>
+      <c r="E4" s="153"/>
+      <c r="F4" s="143" t="s">
         <v>6</v>
       </c>
-      <c r="G4" s="104"/>
-      <c r="H4" s="85"/>
-      <c r="I4" s="114"/>
-      <c r="J4" s="115"/>
+      <c r="G4" s="144"/>
+      <c r="H4" s="96"/>
+      <c r="I4" s="154"/>
+      <c r="J4" s="155"/>
     </row>
-    <row r="5" spans="1:10" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="116" t="s">
+    <row r="5" spans="1:10" customFormat="1" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A5" s="131" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="117"/>
-      <c r="C5" s="89"/>
-      <c r="D5" s="118"/>
-      <c r="E5" s="119"/>
+      <c r="B5" s="132"/>
+      <c r="C5" s="100"/>
+      <c r="D5" s="133"/>
+      <c r="E5" s="134"/>
       <c r="F5" s="3"/>
       <c r="G5" s="4"/>
-      <c r="H5" s="89"/>
-      <c r="I5" s="118"/>
-      <c r="J5" s="119"/>
+      <c r="H5" s="100"/>
+      <c r="I5" s="133"/>
+      <c r="J5" s="134"/>
     </row>
-    <row r="6" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="7" spans="1:10" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="120" t="s">
+    <row r="6" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.45"/>
+    <row r="7" spans="1:10" ht="33.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A7" s="135" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="121"/>
-      <c r="C7" s="121"/>
-      <c r="D7" s="121"/>
-      <c r="E7" s="122"/>
-      <c r="F7" s="123" t="s">
+      <c r="B7" s="136"/>
+      <c r="C7" s="136"/>
+      <c r="D7" s="136"/>
+      <c r="E7" s="137"/>
+      <c r="F7" s="138" t="s">
         <v>40</v>
       </c>
-      <c r="G7" s="124"/>
-      <c r="H7" s="124"/>
-      <c r="I7" s="124"/>
-      <c r="J7" s="125"/>
+      <c r="G7" s="139"/>
+      <c r="H7" s="139"/>
+      <c r="I7" s="139"/>
+      <c r="J7" s="140"/>
     </row>
-    <row r="8" spans="1:10" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" ht="25.3" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A8" s="5" t="s">
         <v>11</v>
       </c>
@@ -2447,38 +2447,38 @@
       <c r="E8" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="F8" s="126" t="s">
+      <c r="F8" s="115" t="s">
         <v>16</v>
       </c>
-      <c r="G8" s="127"/>
-      <c r="H8" s="128" t="s">
+      <c r="G8" s="116"/>
+      <c r="H8" s="117" t="s">
         <v>17</v>
       </c>
-      <c r="I8" s="129"/>
+      <c r="I8" s="118"/>
       <c r="J8" s="9" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="130"/>
-      <c r="B9" s="132"/>
-      <c r="C9" s="132"/>
-      <c r="D9" s="135"/>
-      <c r="E9" s="138"/>
+    <row r="9" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="119"/>
+      <c r="B9" s="121"/>
+      <c r="C9" s="121"/>
+      <c r="D9" s="124"/>
+      <c r="E9" s="127"/>
       <c r="F9" s="10" t="s">
         <v>19</v>
       </c>
       <c r="G9" s="26"/>
-      <c r="H9" s="141"/>
-      <c r="I9" s="141"/>
-      <c r="J9" s="142"/>
+      <c r="H9" s="130"/>
+      <c r="I9" s="130"/>
+      <c r="J9" s="101"/>
     </row>
-    <row r="10" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="130"/>
-      <c r="B10" s="133"/>
-      <c r="C10" s="133"/>
-      <c r="D10" s="136"/>
-      <c r="E10" s="139"/>
+    <row r="10" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="119"/>
+      <c r="B10" s="122"/>
+      <c r="C10" s="122"/>
+      <c r="D10" s="125"/>
+      <c r="E10" s="128"/>
       <c r="F10" s="11" t="s">
         <v>20</v>
       </c>
@@ -2487,14 +2487,14 @@
         <v>37</v>
       </c>
       <c r="I10" s="29"/>
-      <c r="J10" s="143"/>
+      <c r="J10" s="102"/>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" s="130"/>
-      <c r="B11" s="133"/>
-      <c r="C11" s="133"/>
-      <c r="D11" s="136"/>
-      <c r="E11" s="139"/>
+    <row r="11" spans="1:10" ht="15" x14ac:dyDescent="0.4">
+      <c r="A11" s="119"/>
+      <c r="B11" s="122"/>
+      <c r="C11" s="122"/>
+      <c r="D11" s="125"/>
+      <c r="E11" s="128"/>
       <c r="F11" s="12" t="s">
         <v>33</v>
       </c>
@@ -2503,14 +2503,14 @@
         <v>36</v>
       </c>
       <c r="I11" s="34"/>
-      <c r="J11" s="143"/>
+      <c r="J11" s="102"/>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A12" s="130"/>
-      <c r="B12" s="133"/>
-      <c r="C12" s="133"/>
-      <c r="D12" s="136"/>
-      <c r="E12" s="139"/>
+    <row r="12" spans="1:10" ht="15" x14ac:dyDescent="0.4">
+      <c r="A12" s="119"/>
+      <c r="B12" s="122"/>
+      <c r="C12" s="122"/>
+      <c r="D12" s="125"/>
+      <c r="E12" s="128"/>
       <c r="F12" s="12" t="s">
         <v>35</v>
       </c>
@@ -2519,14 +2519,14 @@
         <v>34</v>
       </c>
       <c r="I12" s="29"/>
-      <c r="J12" s="143"/>
+      <c r="J12" s="102"/>
     </row>
-    <row r="13" spans="1:10" ht="25.5" x14ac:dyDescent="0.25">
-      <c r="A13" s="130"/>
-      <c r="B13" s="133"/>
-      <c r="C13" s="133"/>
-      <c r="D13" s="136"/>
-      <c r="E13" s="139"/>
+    <row r="13" spans="1:10" ht="24.9" x14ac:dyDescent="0.4">
+      <c r="A13" s="119"/>
+      <c r="B13" s="122"/>
+      <c r="C13" s="122"/>
+      <c r="D13" s="125"/>
+      <c r="E13" s="128"/>
       <c r="F13" s="13" t="s">
         <v>21</v>
       </c>
@@ -2535,14 +2535,14 @@
         <v>38</v>
       </c>
       <c r="I13" s="29"/>
-      <c r="J13" s="143"/>
+      <c r="J13" s="102"/>
     </row>
-    <row r="14" spans="1:10" ht="18" x14ac:dyDescent="0.25">
-      <c r="A14" s="130"/>
-      <c r="B14" s="133"/>
-      <c r="C14" s="133"/>
-      <c r="D14" s="136"/>
-      <c r="E14" s="139"/>
+    <row r="14" spans="1:10" ht="17.149999999999999" x14ac:dyDescent="0.4">
+      <c r="A14" s="119"/>
+      <c r="B14" s="122"/>
+      <c r="C14" s="122"/>
+      <c r="D14" s="125"/>
+      <c r="E14" s="128"/>
       <c r="F14" s="30" t="s">
         <v>32</v>
       </c>
@@ -2551,30 +2551,30 @@
         <v>39</v>
       </c>
       <c r="I14" s="34"/>
-      <c r="J14" s="143"/>
+      <c r="J14" s="102"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A15" s="130"/>
-      <c r="B15" s="133"/>
-      <c r="C15" s="133"/>
-      <c r="D15" s="136"/>
-      <c r="E15" s="139"/>
-      <c r="F15" s="152"/>
-      <c r="G15" s="153"/>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A15" s="119"/>
+      <c r="B15" s="122"/>
+      <c r="C15" s="122"/>
+      <c r="D15" s="125"/>
+      <c r="E15" s="128"/>
+      <c r="F15" s="111"/>
+      <c r="G15" s="112"/>
       <c r="H15" s="31" t="s">
         <v>22</v>
       </c>
       <c r="I15" s="40"/>
-      <c r="J15" s="144"/>
+      <c r="J15" s="103"/>
     </row>
-    <row r="16" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="131"/>
-      <c r="B16" s="134"/>
-      <c r="C16" s="134"/>
-      <c r="D16" s="137"/>
-      <c r="E16" s="140"/>
-      <c r="F16" s="154"/>
-      <c r="G16" s="155"/>
+    <row r="16" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A16" s="120"/>
+      <c r="B16" s="123"/>
+      <c r="C16" s="123"/>
+      <c r="D16" s="126"/>
+      <c r="E16" s="129"/>
+      <c r="F16" s="113"/>
+      <c r="G16" s="114"/>
       <c r="H16" s="32" t="s">
         <v>23</v>
       </c>
@@ -2587,19 +2587,19 @@
         <v>#DIV/0!</v>
       </c>
     </row>
-    <row r="17" spans="1:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="18" spans="1:10" ht="26.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="145" t="s">
+    <row r="17" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.45"/>
+    <row r="18" spans="1:10" ht="25.3" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A18" s="104" t="s">
         <v>24</v>
       </c>
-      <c r="B18" s="146"/>
-      <c r="C18" s="146"/>
-      <c r="D18" s="146"/>
-      <c r="E18" s="147"/>
-      <c r="F18" s="148" t="s">
+      <c r="B18" s="105"/>
+      <c r="C18" s="105"/>
+      <c r="D18" s="105"/>
+      <c r="E18" s="106"/>
+      <c r="F18" s="107" t="s">
         <v>25</v>
       </c>
-      <c r="G18" s="149"/>
+      <c r="G18" s="108"/>
       <c r="H18" s="16" t="s">
         <v>26</v>
       </c>
@@ -2610,7 +2610,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:10" ht="18.899999999999999" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A19" s="18" t="s">
         <v>28</v>
       </c>
@@ -2618,8 +2618,8 @@
       <c r="C19" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="D19" s="150"/>
-      <c r="E19" s="151"/>
+      <c r="D19" s="109"/>
+      <c r="E19" s="110"/>
       <c r="F19" s="21" t="s">
         <v>30</v>
       </c>
@@ -2638,24 +2638,6 @@
     </row>
   </sheetData>
   <mergeCells count="31">
-    <mergeCell ref="J9:J15"/>
-    <mergeCell ref="A18:E18"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="D19:E19"/>
-    <mergeCell ref="F15:G16"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="H8:I8"/>
-    <mergeCell ref="A9:A16"/>
-    <mergeCell ref="B9:B16"/>
-    <mergeCell ref="C9:C16"/>
-    <mergeCell ref="D9:D16"/>
-    <mergeCell ref="E9:E16"/>
-    <mergeCell ref="H9:I9"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="C5:E5"/>
-    <mergeCell ref="H5:J5"/>
-    <mergeCell ref="A7:E7"/>
-    <mergeCell ref="F7:J7"/>
     <mergeCell ref="A2:B2"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A4:B4"/>
@@ -2669,6 +2651,24 @@
     <mergeCell ref="C4:E4"/>
     <mergeCell ref="F4:G4"/>
     <mergeCell ref="H4:J4"/>
+    <mergeCell ref="A5:B5"/>
+    <mergeCell ref="C5:E5"/>
+    <mergeCell ref="H5:J5"/>
+    <mergeCell ref="A7:E7"/>
+    <mergeCell ref="F7:J7"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="H8:I8"/>
+    <mergeCell ref="A9:A16"/>
+    <mergeCell ref="B9:B16"/>
+    <mergeCell ref="C9:C16"/>
+    <mergeCell ref="D9:D16"/>
+    <mergeCell ref="E9:E16"/>
+    <mergeCell ref="H9:I9"/>
+    <mergeCell ref="J9:J15"/>
+    <mergeCell ref="A18:E18"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="F15:G16"/>
   </mergeCells>
   <conditionalFormatting sqref="A1:XFD6 K7:XFD1048576 A17:J17 A20:J1048576">
     <cfRule type="cellIs" dxfId="9" priority="17" operator="equal">
@@ -2720,6 +2720,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100EFE0C39B20CFE747B2EDBEF1A424A9C1" ma:contentTypeVersion="14" ma:contentTypeDescription="Creare un nuovo documento." ma:contentTypeScope="" ma:versionID="fc5d43efe255f0326fdf88779d9e8cc0">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="71e126cb-1963-4e7b-b13a-15d2f64f78e9" xmlns:ns3="f41f4605-e15c-4135-bd96-d3970596b173" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c67b044c92a952204dd5da40bf3ff3c1" ns2:_="" ns3:_="">
     <xsd:import namespace="71e126cb-1963-4e7b-b13a-15d2f64f78e9"/>
@@ -2948,15 +2957,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -2969,13 +2969,39 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D115D133-EAEB-4443-A9C1-E625D5CAD6FB}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6DDD1081-A99F-47A1-A775-3B0BDB49EF44}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6DDD1081-A99F-47A1-A775-3B0BDB49EF44}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D115D133-EAEB-4443-A9C1-E625D5CAD6FB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="71e126cb-1963-4e7b-b13a-15d2f64f78e9"/>
+    <ds:schemaRef ds:uri="f41f4605-e15c-4135-bd96-d3970596b173"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{74AE7FB1-BBFF-43EB-A790-C6A1DD7213BF}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{74AE7FB1-BBFF-43EB-A790-C6A1DD7213BF}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="f41f4605-e15c-4135-bd96-d3970596b173"/>
+    <ds:schemaRef ds:uri="71e126cb-1963-4e7b-b13a-15d2f64f78e9"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>